--- a/Test/ExpsDescription.xlsx
+++ b/Test/ExpsDescription.xlsx
@@ -1,151 +1,46 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\slongueira\Desktop\MyTryPy2\Test\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EF1A4E9-5918-4850-BE5B-2312F4E974BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
-  <si>
-    <t>ExpId</t>
-  </si>
-  <si>
-    <t>TribuId</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>DaqFile</t>
-  </si>
-  <si>
-    <t>MotorFile</t>
-  </si>
-  <si>
-    <t>Capacitorld</t>
-  </si>
-  <si>
-    <t>RloadId</t>
-  </si>
-  <si>
-    <t>ContactForce</t>
-  </si>
-  <si>
-    <t>InitialPosition</t>
-  </si>
-  <si>
-    <t>FinalPosition</t>
-  </si>
-  <si>
-    <t>ContactPosition</t>
-  </si>
-  <si>
-    <t>CurrentTh</t>
-  </si>
-  <si>
-    <t>Latency</t>
-  </si>
-  <si>
-    <t>MeasuredParameterMotor</t>
-  </si>
-  <si>
-    <t>SampleRateDAQ(Hz)</t>
-  </si>
-  <si>
-    <t>SampleRateMotor(Hz)</t>
-  </si>
-  <si>
-    <t>SamplestoReadDAQ</t>
-  </si>
-  <si>
-    <t>SamplestoReadMotor</t>
-  </si>
-  <si>
-    <t>ReadingTime (s)</t>
-  </si>
-  <si>
-    <t>Electrode rGO</t>
-  </si>
-  <si>
-    <t>MotorSpeedDown(m/s)</t>
-  </si>
-  <si>
-    <t>MotorAccelerationDown(m/s)</t>
-  </si>
-  <si>
-    <t>MotorDecelerationDown(m/s)</t>
-  </si>
-  <si>
-    <t>Motor Speed Up(m/s)</t>
-  </si>
-  <si>
-    <t>Motor AccelerationUp(m/s)</t>
-  </si>
-  <si>
-    <t>MotorDecelerationUp(m/s)</t>
-  </si>
-  <si>
-    <t>MotorForceMax</t>
-  </si>
-  <si>
-    <t>T2(ms) contact time</t>
-  </si>
-  <si>
-    <t>T1(ms)</t>
-  </si>
-  <si>
-    <t>Comments</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="3">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <name val="Liberation Sans"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Liberation Sans"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -167,11 +62,11 @@
     </border>
     <border>
       <left style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
+        <color theme="4" tint="0.3999755851924192"/>
       </left>
       <right/>
       <top style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
+        <color theme="4" tint="0.3999755851924192"/>
       </top>
       <bottom/>
       <diagonal/>
@@ -180,7 +75,7 @@
       <left/>
       <right/>
       <top style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
+        <color theme="4" tint="0.3999755851924192"/>
       </top>
       <bottom/>
       <diagonal/>
@@ -197,7 +92,7 @@
     <border>
       <left/>
       <right style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
+        <color theme="4" tint="0.3999755851924192"/>
       </right>
       <top style="thin">
         <color rgb="FF44B3E1"/>
@@ -210,11 +105,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -222,17 +117,17 @@
   <dxfs count="1">
     <dxf>
       <font>
-        <b/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <b val="1"/>
         <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
+        <condense val="0"/>
+        <color rgb="FFFFFFFF"/>
+        <extend val="0"/>
+        <sz val="11"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
       </font>
       <fill>
         <patternFill patternType="solid">
@@ -243,51 +138,111 @@
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:AD10" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="A1:AD10" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:AD10" headerRowCount="1" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A1:AD10"/>
   <tableColumns count="30">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ExpId"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="TribuId"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Date"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="DaqFile"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="MotorFile"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Capacitorld"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="RloadId"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="ContactForce"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="InitialPosition"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="FinalPosition"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="ContactPosition"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="CurrentTh"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Latency"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="MeasuredParameterMotor"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="SampleRateDAQ(Hz)"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="SampleRateMotor(Hz)"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="SamplestoReadDAQ"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="SamplestoReadMotor"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="ReadingTime (s)"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Electrode rGO"/>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="MotorSpeedDown(m/s)"/>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="MotorAccelerationDown(m/s)"/>
-    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="MotorDecelerationDown(m/s)"/>
-    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="Motor Speed Up(m/s)"/>
-    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="Motor AccelerationUp(m/s)"/>
-    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="MotorDecelerationUp(m/s)"/>
-    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name="MotorForceMax"/>
-    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="T2(ms) contact time"/>
-    <tableColumn id="29" xr3:uid="{00000000-0010-0000-0000-00001D000000}" name="T1(ms)"/>
-    <tableColumn id="30" xr3:uid="{00000000-0010-0000-0000-00001E000000}" name="Comments"/>
+    <tableColumn id="1" name="ExpId"/>
+    <tableColumn id="2" name="TribuId"/>
+    <tableColumn id="3" name="Date"/>
+    <tableColumn id="4" name="DaqFile"/>
+    <tableColumn id="5" name="MotorFile"/>
+    <tableColumn id="6" name="Capacitorld"/>
+    <tableColumn id="7" name="RloadId"/>
+    <tableColumn id="8" name="ContactForce"/>
+    <tableColumn id="9" name="InitialPosition"/>
+    <tableColumn id="10" name="FinalPosition"/>
+    <tableColumn id="11" name="ContactPosition"/>
+    <tableColumn id="12" name="CurrentTh"/>
+    <tableColumn id="13" name="Latency"/>
+    <tableColumn id="14" name="MeasuredParameterMotor"/>
+    <tableColumn id="15" name="SampleRateDAQ(Hz)"/>
+    <tableColumn id="16" name="SampleRateMotor(Hz)"/>
+    <tableColumn id="17" name="SamplestoReadDAQ"/>
+    <tableColumn id="18" name="SamplestoReadMotor"/>
+    <tableColumn id="19" name="ReadingTime (s)"/>
+    <tableColumn id="20" name="Electrode rGO"/>
+    <tableColumn id="21" name="MotorSpeedDown(m/s)"/>
+    <tableColumn id="22" name="MotorAccelerationDown(m/s)"/>
+    <tableColumn id="23" name="MotorDecelerationDown(m/s)"/>
+    <tableColumn id="24" name="Motor Speed Up(m/s)"/>
+    <tableColumn id="25" name="Motor AccelerationUp(m/s)"/>
+    <tableColumn id="26" name="MotorDecelerationUp(m/s)"/>
+    <tableColumn id="27" name="MotorForceMax"/>
+    <tableColumn id="28" name="T2(ms) contact time"/>
+    <tableColumn id="29" name="T1(ms)"/>
+    <tableColumn id="30" name="Comments"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -555,133 +510,324 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AD1"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AD10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="19" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="23" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="18" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="20" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="17" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="19" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="16" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="20" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="27" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="27" customWidth="1"/>
-    <col min="24" max="24" width="20" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="26" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="25" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="20" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="7" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="9" bestFit="1" customWidth="1"/>
+    <col width="9" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="8" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="4"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="19" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="12" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="8" bestFit="1" customWidth="1" min="7" max="7"/>
+    <col width="13" bestFit="1" customWidth="1" min="8" max="8"/>
+    <col width="16" bestFit="1" customWidth="1" min="9" max="9"/>
+    <col width="14" bestFit="1" customWidth="1" min="10" max="10"/>
+    <col width="16" bestFit="1" customWidth="1" min="11" max="11"/>
+    <col width="10" bestFit="1" customWidth="1" min="12" max="12"/>
+    <col width="8" bestFit="1" customWidth="1" min="13" max="13"/>
+    <col width="23" bestFit="1" customWidth="1" min="14" max="14"/>
+    <col width="18" bestFit="1" customWidth="1" min="15" max="15"/>
+    <col width="20" bestFit="1" customWidth="1" min="16" max="16"/>
+    <col width="17" bestFit="1" customWidth="1" min="17" max="17"/>
+    <col width="19" bestFit="1" customWidth="1" min="18" max="18"/>
+    <col width="16" bestFit="1" customWidth="1" min="19" max="19"/>
+    <col width="14" bestFit="1" customWidth="1" min="20" max="20"/>
+    <col width="20" bestFit="1" customWidth="1" min="21" max="21"/>
+    <col width="27" bestFit="1" customWidth="1" min="22" max="22"/>
+    <col width="27" customWidth="1" min="23" max="23"/>
+    <col width="20" bestFit="1" customWidth="1" min="24" max="24"/>
+    <col width="26" bestFit="1" customWidth="1" min="25" max="25"/>
+    <col width="25" bestFit="1" customWidth="1" min="26" max="26"/>
+    <col width="14" bestFit="1" customWidth="1" min="27" max="27"/>
+    <col width="20" bestFit="1" customWidth="1" min="28" max="28"/>
+    <col width="7" bestFit="1" customWidth="1" min="29" max="29"/>
+    <col width="9" bestFit="1" customWidth="1" min="30" max="30"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="S1" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="T1" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="U1" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="V1" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="W1" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="X1" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="Y1" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="Z1" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA1" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="AB1" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="AC1" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="AD1" s="4" t="s">
-        <v>29</v>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ExpId</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>TribuId</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>DaqFile</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>MotorFile</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Capacitorld</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>RloadId</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>ContactForce</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>InitialPosition</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>FinalPosition</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>ContactPosition</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>CurrentTh</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>Latency</t>
+        </is>
+      </c>
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>MeasuredParameterMotor</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>SampleRateDAQ(Hz)</t>
+        </is>
+      </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
+          <t>SampleRateMotor(Hz)</t>
+        </is>
+      </c>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>SamplestoReadDAQ</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="inlineStr">
+        <is>
+          <t>SamplestoReadMotor</t>
+        </is>
+      </c>
+      <c r="S1" s="3" t="inlineStr">
+        <is>
+          <t>ReadingTime (s)</t>
+        </is>
+      </c>
+      <c r="T1" s="3" t="inlineStr">
+        <is>
+          <t>Electrode rGO</t>
+        </is>
+      </c>
+      <c r="U1" s="3" t="inlineStr">
+        <is>
+          <t>MotorSpeedDown(m/s)</t>
+        </is>
+      </c>
+      <c r="V1" s="3" t="inlineStr">
+        <is>
+          <t>MotorAccelerationDown(m/s)</t>
+        </is>
+      </c>
+      <c r="W1" s="3" t="inlineStr">
+        <is>
+          <t>MotorDecelerationDown(m/s)</t>
+        </is>
+      </c>
+      <c r="X1" s="3" t="inlineStr">
+        <is>
+          <t>Motor Speed Up(m/s)</t>
+        </is>
+      </c>
+      <c r="Y1" s="3" t="inlineStr">
+        <is>
+          <t>Motor AccelerationUp(m/s)</t>
+        </is>
+      </c>
+      <c r="Z1" s="3" t="inlineStr">
+        <is>
+          <t>MotorDecelerationUp(m/s)</t>
+        </is>
+      </c>
+      <c r="AA1" s="3" t="inlineStr">
+        <is>
+          <t>MotorForceMax</t>
+        </is>
+      </c>
+      <c r="AB1" s="3" t="inlineStr">
+        <is>
+          <t>T2(ms) contact time</t>
+        </is>
+      </c>
+      <c r="AC1" s="3" t="inlineStr">
+        <is>
+          <t>T1(ms)</t>
+        </is>
+      </c>
+      <c r="AD1" s="4" t="inlineStr">
+        <is>
+          <t>Comments</t>
+        </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2508-A-2</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>25082025_114716</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>DAQ-2508-A-2.pkl</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Motor-2508-A-2.csv</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2508-A-3</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>25082025_114904</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>DAQ-2508-A-3.pkl</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Motor-2508-A-3.csv</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2508-A-4</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>25082025_114928</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>DAQ-2508-A-4.pkl</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Motor-2508-A-4.csv</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+    </row>
+    <row r="5"/>
+    <row r="6"/>
+    <row r="7"/>
+    <row r="8"/>
+    <row r="9"/>
+    <row r="10"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/Test/ExpsDescription.xlsx
+++ b/Test/ExpsDescription.xlsx
@@ -210,7 +210,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:AD10" headerRowCount="1" totalsRowShown="0" headerRowDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:AD16" headerRowCount="1" totalsRowShown="0" headerRowDxfId="0">
   <autoFilter ref="A1:AD10"/>
   <tableColumns count="30">
     <tableColumn id="1" name="ExpId"/>
@@ -515,7 +515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD10"/>
+  <dimension ref="A1:AD16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="9" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -792,42 +792,420 @@
           <t>Motor-2508-A-4.csv</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr"/>
-    </row>
-    <row r="5"/>
-    <row r="6"/>
-    <row r="7"/>
-    <row r="8"/>
-    <row r="9"/>
-    <row r="10"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2508-c-1</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>25082025_125738</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>DAQ-2508-c-1.pkl</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Motor-2508-c-1.csv</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2508-F-3</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>25082025_140729</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>DAQ-2508-F-3.pkl</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Motor-2508-F-3.csv</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2508-F-3</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>25082025_141356</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>DAQ-2508-F-3.pkl</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Motor-2508-F-3.csv</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2508-F-3</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>25082025_153102</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>DAQ-2508-F-3.pkl</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Motor-2508-F-3.csv</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2508-F-3</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>25082025_153425</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>DAQ-2508-F-3.pkl</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Motor-2508-F-3.csv</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2508-F-3</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>25082025_154829</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>DAQ-2508-F-3.pkl</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Motor-2508-F-3.csv</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2508-F-3</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>25082025_155351</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>DAQ-2508-F-3.pkl</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Motor-2508-F-3.csv</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2508-F-3</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>25082025_155728</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>DAQ-2508-F-3.pkl</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Motor-2508-F-3.csv</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2508-F-3</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>25082025_155928</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>DAQ-2508-F-3.pkl</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Motor-2508-F-3.csv</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2508-F-3</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>25082025_160506</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>DAQ-2508-F-3.pkl</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Motor-2508-F-3.csv</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2508-F-3</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>25082025_161035</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>DAQ-2508-F-3.pkl</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Motor-2508-F-3.csv</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2508-F-3</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>25082025_161333</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>DAQ-2508-F-3.pkl</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Motor-2508-F-3.csv</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
